--- a/supermarkets.xlsx
+++ b/supermarkets.xlsx
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="251">
   <si>
     <t>supermarket_name</t>
   </si>
@@ -85,523 +85,539 @@
     <t>أسواق فتح الله</t>
   </si>
   <si>
+    <t>37 عمرو بن العاص، مدينة نصر، القاهرة</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/aswaqfathallamarket/posts/%D8%A3%D8%B7%D9%84%D8%A8-15260-%D9%88-%D8%B7%D9%84%D8%A8%D8%A7%D8%AA%D9%83-%D8%AA%D8%AC%D9%8A%D9%84%D9%83-%D9%84%D8%AD%D8%AF-%D8%A8%D8%A7%D8%A8-%D8%A8%D9%8A%D8%AA%D9%83-%D9%81%D8%AA%D8%AD_%D8%A7%D9%84%D9%84%D9%87_%D8%AF%D8%A7%D9%8A%D9%85%D8%A7_%D8%A7%D9%84%D8%A3%D9%82%D8%B1%D8%A8_%D9%88_%D8%A7%D9%84%D8%A3%D9%88%D9%81%D8%B1/2195360477437969/</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/أسواق+فتح+الله</t>
+  </si>
+  <si>
+    <t>https://fathalla.com</t>
+  </si>
+  <si>
+    <t>اكسبشن ماركت</t>
+  </si>
+  <si>
+    <t>01200 9622 2</t>
+  </si>
+  <si>
+    <t>14 ش جمال عبد الناصر، المهندسين، الجيزة</t>
+  </si>
+  <si>
+    <t>https://exception.com.eg/</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/اكسبشن+ماركت</t>
+  </si>
+  <si>
+    <t>التوحيد والنور</t>
+  </si>
+  <si>
+    <t>16119 </t>
+  </si>
+  <si>
+    <t>111 ش التوفيقية، الدقي، الجيزة</t>
+  </si>
+  <si>
+    <t>https://tawheedwnour.com/</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/التوحيد+والنور</t>
+  </si>
+  <si>
+    <t>الراية</t>
+  </si>
+  <si>
+    <t>42 ش السلطان حسين، المنيل، القاهرة</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/AlRayahMarketEg/</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/أسواق+الراية</t>
+  </si>
+  <si>
+    <t>https://alrayah-market.com/</t>
+  </si>
+  <si>
+    <t>السلطان ماركت</t>
+  </si>
+  <si>
+    <t>17 ش السلطان حسين، المنيل، القاهرة</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/Alsultan.Hypermarket/</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/السلطان+ماركت</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>العبد</t>
+  </si>
+  <si>
+    <r>
+      <t>16437</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>123 ش شبرا، شبرا، القاهرة</t>
+  </si>
+  <si>
+    <t>https://elabdfoods.com/</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/حلواني+العبد</t>
+  </si>
+  <si>
+    <t>العثيم</t>
+  </si>
+  <si>
+    <t>23 ش أحمد حلمي، المهندسين، الجيزة</t>
+  </si>
+  <si>
+    <t>https://othaimmarkets.com</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/أسواق+العثيم</t>
+  </si>
+  <si>
+    <t>https://www.othaimmarkets.com/</t>
+  </si>
+  <si>
+    <t>ألفا ماركت</t>
+  </si>
+  <si>
+    <t>15 ش أحمد حلمي، المهندسين، الجيزة</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/AlfaMarketeg/#:~:text=in%20no%20time.-,%F0%9F%93%9E%2015120%20%F0%9F%8C%90%20www.alfamarketeg.com%20%F0%9F%93%B1%20Download%20Alfa,Market%20App%20%2D%20%D8%AD%D9%85%D9%84%20%D8%A7%D9%84%D8%A7%D8%A8%D9%84%D9%83%D9%8A%D8%B4%D9%86%20%23NoTricksJustTreats</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/ألفا+ماركت</t>
+  </si>
+  <si>
+    <t>www.alfamarketeg.com</t>
+  </si>
+  <si>
+    <t>الفرجاني</t>
+  </si>
+  <si>
+    <t>27 ش العشرين، مدينة نصر، القاهرة</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/marketelfergany/?locale=ar_AR</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/أسواق+الفرجاني</t>
+  </si>
+  <si>
+    <t>- (info@el-fergany.com)</t>
+  </si>
+  <si>
+    <t>المحلاوي ماركت</t>
+  </si>
+  <si>
+    <t>01155488626</t>
+  </si>
+  <si>
+    <t>11 ش الميرغني، العباسية، القاهرة</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/elmahallawy.co/posts/%D8%B5%D8%A8%D8%A7%D8%AD-%D8%A7%D9%84%D8%AD%D9%84%D9%88%D9%8A%D8%A7%D8%AA%D9%85%D8%AA%D9%88%D9%81%D8%B1-%D8%AF%D8%A7%D8%AE%D9%84-%D9%83%D9%84-%D9%81%D8%B1%D9%88%D8%B9%D9%86%D8%A7-%D9%88%D9%85%D8%AA%D9%86%D8%B3%D9%88%D8%B4-%D8%B9%D8%B1%D9%88%D8%B6%D9%86%D8%A7-%D8%AF%D8%A7%D8%AE%D9%84-%D9%81%D8%B1%D9%88%D8%B9%D9%86%D8%A7-%D9%81%D9%82%D8%B7-%D9%88%D9%87%D9%8A%D9%81%D8%B1%D8%B9-%D9%85%D9%83%D8%B1%D9%85-%D8%B9%D8%A8%D9%8A/1132859925536996/#:~:text=q%3D30.010053634643555%2C31.42715072,%D8%A7%D9%84%D9%85%D9%87%D9%86%D8%AF%D8%B3%D9%8A%D9%86%20%D9%88%D8%A7%D8%AA%D8%B3%20%D8%A7%D8%A8%2001010410433%2001100433920</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/المحلاوي+ماركت</t>
+  </si>
+  <si>
+    <t>https://elmahllawy.com/</t>
+  </si>
+  <si>
+    <t>المرشدي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">١٦٩٠١ </t>
+  </si>
+  <si>
+    <t>20 ش صقر قريش، المهندسين، الجيزة</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/Al.morshedy/?locale=ar_AR</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/أسواق+المرشدي</t>
+  </si>
+  <si>
+    <t>almorshedymarts.net</t>
+  </si>
+  <si>
+    <t>اوسكار</t>
+  </si>
+  <si>
+    <t>35 ش أحمد حلمي، المهندسين، الجيزة</t>
+  </si>
+  <si>
+    <t>https://oscarstores.com</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/اوسكار+جراند+ستورز</t>
+  </si>
+  <si>
+    <t>https://www.oscarstores.com/</t>
+  </si>
+  <si>
+    <t>أولاد رجب</t>
+  </si>
+  <si>
+    <t>01011186954</t>
+  </si>
+  <si>
+    <t>14 ش أحمد حلمي، المهندسين، الجيزة</t>
+  </si>
+  <si>
+    <t>https://awladragab.com</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/أولاد+رجب</t>
+  </si>
+  <si>
+    <t>www.awladragab.com</t>
+  </si>
+  <si>
+    <t>ايتوال</t>
+  </si>
+  <si>
+    <t>16 ش شبرا، القاهرة</t>
+  </si>
+  <si>
+    <t>https://etoileeg.online/</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/حلواني+ايتوال</t>
+  </si>
+  <si>
+    <t>بنده Panda</t>
+  </si>
+  <si>
+    <t>التجمع الخامس، القاهرة الجديدة</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/1060184590717105/</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/بنده+Panda</t>
+  </si>
+  <si>
+    <t>(تطبيق Panda Egypt)</t>
+  </si>
+  <si>
+    <t>بيت الجملة</t>
+  </si>
+  <si>
+    <t>21 ش العشرين، مدينة نصر، القاهرة</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/BeitElGomla/posts/%D8%AF%D9%84%D9%88%D9%82%D8%AA%D9%8A-%D9%81%D9%8A-%D8%A8%D9%8A%D8%AA-%D8%A7%D9%84%D8%AC%D9%85%D9%84%D8%A9-%D8%AE%D8%B7-%D8%B3%D8%A7%D8%AE%D9%86-%D9%85%D9%88%D8%AD%D8%AF-15677%EF%B8%8F%D9%84%D9%83%D9%84-%D8%A7%D9%84%D9%81%D8%B1%D9%88%D8%B9-%D9%81%D9%8A-%D8%A7%D9%84%D9%82%D8%A7%D9%87%D8%B1%D8%A9-%D9%88%D8%A7%D9%84%D8%A3%D8%B3%D9%83%D9%86%D8%AF%D8%B1%D9%8A%D8%A9%D9%85%D8%B3%D8%AA%D9%86%D9%8A%D9%86%D9%83/1411072232605043/?locale=ar_AR</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/بيت+الجملة</t>
+  </si>
+  <si>
+    <t>https://www.bgomla.com/</t>
+  </si>
+  <si>
+    <t>بيم</t>
+  </si>
+  <si>
+    <t>01010337248</t>
+  </si>
+  <si>
+    <t>https://bim.eg</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/بيم+ماركت</t>
+  </si>
+  <si>
+    <t>https://www.bim.eg/</t>
+  </si>
+  <si>
+    <t>تسيباس</t>
+  </si>
+  <si>
+    <t>19918</t>
+  </si>
+  <si>
+    <t>https://tseppas.com</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/تسيباس</t>
+  </si>
+  <si>
+    <t>https://www.tseppas.com/</t>
+  </si>
+  <si>
+    <t>جملة ماركت</t>
+  </si>
+  <si>
+    <t>https://gomlamarket.com/</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/جملة+ماركت</t>
+  </si>
+  <si>
+    <t>جيان</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/Geant.eg/posts/your-diet-essentials-are-all-here-at-g%C3%A9ant-%EF%B8%8Ffor-orders-call-us-at-16232-right-no/830856496135388/</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/جيان+ماركت</t>
+  </si>
+  <si>
+    <t>خير زمان</t>
+  </si>
+  <si>
+    <t>16007</t>
+  </si>
+  <si>
+    <t>https://kheirzaman.com</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/خير+زمان</t>
+  </si>
+  <si>
+    <t>https://www.kheirzaman.com/</t>
+  </si>
+  <si>
+    <t>رنين</t>
+  </si>
+  <si>
+    <t>16113</t>
+  </si>
+  <si>
+    <t>https://raneen.com</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/رنين</t>
+  </si>
+  <si>
+    <t>رويال هاوس</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/royalhousesupermarket/?locale=ar_AR#:~:text=Royal%20House%20Supermarket%20is%20the,Hotline%20%3A%2016821%20%F0%9F%93%9E%20.</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/رويال+هاوس</t>
+  </si>
+  <si>
+    <t>زاهر ماركت</t>
+  </si>
+  <si>
+    <t>01111998637</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/ZaherDairy/posts/%D8%A7%D9%81%D8%AA%D8%AA%D8%A7%D8%AD-%D9%81%D8%B1%D8%B9-%D8%A7%D9%84%D8%AA%D8%AC%D9%85%D8%B9-%D8%A7%D9%84%D8%A3%D9%88%D9%84-%D9%85%D8%B3%D8%AA%D9%86%D9%8A%D9%86%D9%83-%D8%AA%D9%86%D9%88%D8%B1%D9%86%D8%A7-%D9%81%D9%8A-%D9%81%D8%B1%D8%B9-%D8%A7%D9%84%D8%AA%D8%AC%D9%85%D8%B9-%D8%A7%D9%84%D8%A3%D9%88%D9%84-%D9%88%D8%AA%D8%B3%D8%AA%D9%85%D8%AA%D8%B9-%D8%A8%D8%AE%D8%B5%D9%85-10-%D8%B9%D9%84%D9%89-%D9%83/892205166518213/#:~:text=.app.goo.-,gl%2Fmtmc7FeLJFCrDbY9A%20%D9%84%D8%AA%D9%81%D8%A7%D8%B5%D9%8A%D9%84%20%D8%A7%D9%83%D8%AA%D8%B1%20%D9%83%D9%84%D9%85%D9%86%D8%A7%20%D8%B9%D9%84%D9%8A%20%3A%F0%9F%93%9E%2019360%20%D8%A7%D9%88%20%D8%A7%D8%A8%D8%B9%D8%AA,Zaher%20%23ZaherMarket%20%23ZaherApp%20%23%D8%B7%D8%A8%D9%8A%D8%B9%D9%8A_%D8%B2%D8%A7%D9%87%D8%B1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/زاهر+ماركت</t>
+  </si>
+  <si>
+    <t>زهران ماركت</t>
+  </si>
+  <si>
+    <t>https://zahranmarket.com</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/زهران+ماركت</t>
+  </si>
+  <si>
+    <t>ساليه سوكريه</t>
+  </si>
+  <si>
+    <t>16 ش شبرا، شبرا، القاهرة</t>
+  </si>
+  <si>
+    <t>https://salesucre.com</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/ساليه+سوكريه</t>
+  </si>
+  <si>
+    <t>سامي سلامة وأولاده</t>
+  </si>
+  <si>
+    <t>01091999207 </t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/Samy.Salama.Sons/#:~:text=%D8%A7%D9%84%D8%AA%D9%88%D9%81%D9%8A%D8%B1%20%D9%8A%D8%A8%D8%AF%D8%A3%20%D9%85%D9%86%20%D9%87%D9%86%D8%A7%20%F0%9F%92%9B,%D8%A8%D8%AC%D9%88%D8%A7%D8%B1%20%D8%A7%D9%84%D9%85%D8%B1%D9%83%D8%B2%20%D8%A7%D9%84%D8%B1%D8%A6%D9%8A%D8%B3%D9%8A%20%F0%9F%93%8D%20%D9%85%D9%8A%D8%AF%D8%A7%D9%86</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/سامي+سلامة</t>
+  </si>
+  <si>
+    <t>سبينيز</t>
+  </si>
+  <si>
+    <t>16005</t>
+  </si>
+  <si>
+    <t>https://spinneys-egypt.com</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/سبينيز</t>
+  </si>
+  <si>
+    <t>spinneys.com (أو التطبيق)</t>
+  </si>
+  <si>
+    <t>سراي ماركت</t>
+  </si>
+  <si>
+    <t>https://saraimarket.com/</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/سراي+ماركت</t>
+  </si>
+  <si>
+    <t>سعودي</t>
+  </si>
+  <si>
+    <t>https://seoudisupermarket.com</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/سعودي+ماركت</t>
+  </si>
+  <si>
+    <t>سنتر شاهين</t>
+  </si>
+  <si>
+    <t>16291</t>
+  </si>
+  <si>
+    <t>https://shaheeneg.com/ar/</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/سنتر+شاهين</t>
+  </si>
+  <si>
+    <t>سوبيكو-Supeco</t>
+  </si>
+  <si>
+    <t>01098322130</t>
+  </si>
+  <si>
+    <t>https://www.supeco.app/index.html</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/سوبيكو+Supeco</t>
+  </si>
+  <si>
+    <t>carrefour.com.eg</t>
+  </si>
+  <si>
+    <t>صيدليات مصر</t>
+  </si>
+  <si>
+    <t>19110</t>
+  </si>
+  <si>
+    <t>https://misr-online.com/</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/صيدليات+مصر</t>
+  </si>
+  <si>
+    <t>صيدلية العزبي</t>
+  </si>
+  <si>
+    <t>19600</t>
+  </si>
+  <si>
+    <t>https://elezabypharmacy.com</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/صيدلية+العزبي</t>
+  </si>
+  <si>
+    <t>el-ezaby.com</t>
+  </si>
+  <si>
+    <t>عرفة</t>
+  </si>
+  <si>
+    <r>
+      <t>19284</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF474747"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>https://arafastores.com/ar/pages/stores?srsltid=AfmBOopwRTVvKz1wCjRW5ZE3-AaQX95UMzS77svBO8zC5qu46O6PhN7L</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/عرفة+جروب</t>
+  </si>
+  <si>
+    <t>كارفور</t>
+  </si>
+  <si>
     <t>16061</t>
   </si>
   <si>
-    <t>37 عمرو بن العاص، مدينة نصر، القاهرة</t>
-  </si>
-  <si>
-    <t>https://fathallahg.com</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/أسواق+فتح+الله</t>
-  </si>
-  <si>
-    <t>https://fathalla.com</t>
-  </si>
-  <si>
-    <t>اكسبشن ماركت</t>
-  </si>
-  <si>
-    <t>16606</t>
-  </si>
-  <si>
-    <t>14 ش جمال عبد الناصر، المهندسين، الجيزة</t>
-  </si>
-  <si>
-    <t>https://exceptionmarket.com</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/اكسبشن+ماركت</t>
-  </si>
-  <si>
-    <t>https://exception.com.eg/</t>
-  </si>
-  <si>
-    <t>التوحيد والنور</t>
-  </si>
-  <si>
-    <t>111 ش التوفيقية، الدقي، الجيزة</t>
+    <t>https://carrefouregypt.com</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/كارفور</t>
+  </si>
+  <si>
+    <t>https://www.carrefour.com.eg/</t>
+  </si>
+  <si>
+    <t>كازيون</t>
+  </si>
+  <si>
+    <t>19609</t>
+  </si>
+  <si>
+    <t>https://okaziooun.com/shop/contact-us/</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/كازيون</t>
+  </si>
+  <si>
+    <t>كتالوج إيفون</t>
+  </si>
+  <si>
+    <t>avon.com.eg</t>
   </si>
   <si>
     <t>غير متوفر</t>
   </si>
   <si>
-    <t>https://www.google.com/maps/search/التوحيد+والنور</t>
-  </si>
-  <si>
-    <t>https://tawheedwnour.com/</t>
-  </si>
-  <si>
-    <t>الراية</t>
-  </si>
-  <si>
-    <t>16500</t>
-  </si>
-  <si>
-    <t>42 ش السلطان حسين، المنيل، القاهرة</t>
-  </si>
-  <si>
-    <t>https://elrayamarket.com</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/أسواق+الراية</t>
-  </si>
-  <si>
-    <t>https://alrayah-market.com/</t>
-  </si>
-  <si>
-    <t>السلطان ماركت</t>
-  </si>
-  <si>
-    <t>19024</t>
-  </si>
-  <si>
-    <t>17 ش السلطان حسين، المنيل، القاهرة</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/السلطان+ماركت</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>العبد</t>
-  </si>
-  <si>
-    <t>16437</t>
-  </si>
-  <si>
-    <t>123 ش شبرا، شبرا، القاهرة</t>
-  </si>
-  <si>
-    <t>https://elabddelivery.com</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/حلواني+العبد</t>
-  </si>
-  <si>
-    <t>العثيم</t>
-  </si>
-  <si>
-    <t>16388</t>
-  </si>
-  <si>
-    <t>23 ش أحمد حلمي، المهندسين، الجيزة</t>
-  </si>
-  <si>
-    <t>https://othaimmarkets.com</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/أسواق+العثيم</t>
-  </si>
-  <si>
-    <t>https://www.othaimmarkets.com/</t>
-  </si>
-  <si>
-    <t>ألفا ماركت</t>
-  </si>
-  <si>
-    <t>19299</t>
-  </si>
-  <si>
-    <t>15 ش أحمد حلمي، المهندسين، الجيزة</t>
-  </si>
-  <si>
-    <t>https://alfa.com.eg</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/ألفا+ماركت</t>
-  </si>
-  <si>
-    <t>www.alfamarketeg.com</t>
-  </si>
-  <si>
-    <t>الفرجاني</t>
-  </si>
-  <si>
-    <t>16055</t>
-  </si>
-  <si>
-    <t>27 ش العشرين، مدينة نصر، القاهرة</t>
-  </si>
-  <si>
-    <t>https://elfergany.com</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/أسواق+الفرجاني</t>
-  </si>
-  <si>
-    <t>- (info@el-fergany.com)</t>
-  </si>
-  <si>
-    <t>المحلاوي ماركت</t>
-  </si>
-  <si>
-    <t>11 ش الميرغني، العباسية، القاهرة</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/المحلاوي+ماركت</t>
-  </si>
-  <si>
-    <t>https://elmahllawy.com/</t>
-  </si>
-  <si>
-    <t>المرشدي</t>
-  </si>
-  <si>
-    <t>16301</t>
-  </si>
-  <si>
-    <t>20 ش صقر قريش، المهندسين، الجيزة</t>
-  </si>
-  <si>
-    <t>https://el-morshedy.com</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/أسواق+المرشدي</t>
-  </si>
-  <si>
-    <t>almorshedymarts.net</t>
-  </si>
-  <si>
-    <t>اوسكار</t>
-  </si>
-  <si>
-    <t>16832</t>
-  </si>
-  <si>
-    <t>35 ش أحمد حلمي، المهندسين، الجيزة</t>
-  </si>
-  <si>
-    <t>https://oscarstores.com</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/اوسكار+جراند+ستورز</t>
-  </si>
-  <si>
-    <t>https://www.oscarstores.com/</t>
-  </si>
-  <si>
-    <t>أولاد رجب</t>
-  </si>
-  <si>
-    <t>19225</t>
-  </si>
-  <si>
-    <t>14 ش أحمد حلمي، المهندسين، الجيزة</t>
-  </si>
-  <si>
-    <t>https://awladragab.com</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/أولاد+رجب</t>
-  </si>
-  <si>
-    <t>www.awladragab.com</t>
-  </si>
-  <si>
-    <t>ايتوال</t>
-  </si>
-  <si>
-    <t>16986</t>
-  </si>
-  <si>
-    <t>16 ش شبرا، القاهرة</t>
-  </si>
-  <si>
-    <t>https://etoile.com.eg</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/حلواني+ايتوال</t>
-  </si>
-  <si>
-    <t>https://etoileeg.online/</t>
-  </si>
-  <si>
-    <t>بنده Panda</t>
-  </si>
-  <si>
-    <t>16544</t>
-  </si>
-  <si>
-    <t>التجمع الخامس، القاهرة الجديدة</t>
-  </si>
-  <si>
-    <t>https://panda.com.eg</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/بنده+Panda</t>
-  </si>
-  <si>
-    <t>(تطبيق Panda Egypt)</t>
-  </si>
-  <si>
-    <t>بيت الجملة</t>
-  </si>
-  <si>
-    <t>15606</t>
-  </si>
-  <si>
-    <t>21 ش العشرين، مدينة نصر، القاهرة</t>
-  </si>
-  <si>
-    <t>https://baitelgomla.com</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/بيت+الجملة</t>
-  </si>
-  <si>
-    <t>https://www.bgomla.com/</t>
-  </si>
-  <si>
-    <t>بيم</t>
-  </si>
-  <si>
-    <t>19663</t>
-  </si>
-  <si>
-    <t>https://bim.eg</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/بيم+ماركت</t>
-  </si>
-  <si>
-    <t>https://www.bim.eg/</t>
-  </si>
-  <si>
-    <t>تسيباس</t>
-  </si>
-  <si>
-    <t>19918</t>
-  </si>
-  <si>
-    <t>https://tseppas.com</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/تسيباس</t>
-  </si>
-  <si>
-    <t>https://www.tseppas.com/</t>
-  </si>
-  <si>
-    <t>جملة ماركت</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/جملة+ماركت</t>
-  </si>
-  <si>
-    <t>https://gomlamarket.com/</t>
-  </si>
-  <si>
-    <t>جيان</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/جيان+ماركت</t>
-  </si>
-  <si>
-    <t>خير زمان</t>
-  </si>
-  <si>
-    <t>16007</t>
-  </si>
-  <si>
-    <t>https://kheirzaman.com</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/خير+زمان</t>
-  </si>
-  <si>
-    <t>https://www.kheirzaman.com/</t>
-  </si>
-  <si>
-    <t>رنين</t>
-  </si>
-  <si>
-    <t>16113</t>
-  </si>
-  <si>
-    <t>https://raneen.com</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/رنين</t>
-  </si>
-  <si>
-    <t>رويال هاوس</t>
-  </si>
-  <si>
-    <t>16761</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/رويال+هاوس</t>
-  </si>
-  <si>
-    <t>زاهر ماركت</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/زاهر+ماركت</t>
-  </si>
-  <si>
-    <t>زهران ماركت</t>
-  </si>
-  <si>
-    <t>16669</t>
-  </si>
-  <si>
-    <t>https://zahranmarket.com</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/زهران+ماركت</t>
-  </si>
-  <si>
-    <t>ساليه سوكريه</t>
-  </si>
-  <si>
-    <t>19649</t>
-  </si>
-  <si>
-    <t>16 ش شبرا، شبرا، القاهرة</t>
-  </si>
-  <si>
-    <t>https://salesucre.com</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/ساليه+سوكريه</t>
-  </si>
-  <si>
-    <t>سامي سلامة وأولاده</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/سامي+سلامة</t>
-  </si>
-  <si>
-    <t>سبينيز</t>
-  </si>
-  <si>
-    <t>16005</t>
-  </si>
-  <si>
-    <t>https://spinneys-egypt.com</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/سبينيز</t>
-  </si>
-  <si>
-    <t>spinneys.com (أو التطبيق)</t>
-  </si>
-  <si>
-    <t>سراي ماركت</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/سراي+ماركت</t>
-  </si>
-  <si>
-    <t>سعودي</t>
-  </si>
-  <si>
-    <t>16116</t>
-  </si>
-  <si>
-    <t>https://seoudisupermarket.com</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/سعودي+ماركت</t>
-  </si>
-  <si>
-    <t>سنتر شاهين</t>
-  </si>
-  <si>
-    <t>16291</t>
-  </si>
-  <si>
-    <t>https://centershaheen.com</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/سنتر+شاهين</t>
-  </si>
-  <si>
-    <t>سوبيكو-Supeco</t>
-  </si>
-  <si>
-    <t>https://carrefouregypt.com</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/سوبيكو+Supeco</t>
-  </si>
-  <si>
-    <t>carrefour.com.eg</t>
-  </si>
-  <si>
-    <t>صيدليات مصر</t>
-  </si>
-  <si>
-    <t>19110</t>
-  </si>
-  <si>
-    <t>https://misrpharmacies.com</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/صيدليات+مصر</t>
-  </si>
-  <si>
-    <t>صيدلية العزبي</t>
-  </si>
-  <si>
-    <t>19600</t>
-  </si>
-  <si>
-    <t>https://elezabypharmacy.com</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/صيدلية+العزبي</t>
-  </si>
-  <si>
-    <t>el-ezaby.com</t>
-  </si>
-  <si>
-    <t>عرفة</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/عرفة+جروب</t>
-  </si>
-  <si>
-    <t>كارفور</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/كارفور</t>
-  </si>
-  <si>
-    <t>https://www.carrefour.com.eg/</t>
-  </si>
-  <si>
-    <t>كازيون</t>
-  </si>
-  <si>
-    <t>19609</t>
-  </si>
-  <si>
-    <t>https://kazyon.com</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/search/كازيون</t>
-  </si>
-  <si>
-    <t>كتالوج إيفون</t>
-  </si>
-  <si>
-    <t>https://eg.avon.com</t>
-  </si>
-  <si>
-    <t>avon.com.eg</t>
-  </si>
-  <si>
     <t>كتالوج ماى واى</t>
   </si>
   <si>
-    <t>19799</t>
-  </si>
-  <si>
-    <t>https://mywayegypt.com</t>
+    <t>https://mywayegy.co/</t>
   </si>
   <si>
     <t>https://www.google.com/maps/search/ماي+واي</t>
@@ -610,10 +626,10 @@
     <t>لولو</t>
   </si>
   <si>
-    <t>19956</t>
-  </si>
-  <si>
-    <t>https://luluhypermarket.com</t>
+    <t>0225983555</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/LuLuHypermarketEG/?locale=ar_AR#:~:text=%D8%AA%D9%82%D8%AF%D8%B1%20%D8%AA%D8%AA%D9%88%D8%A7%D8%B5%D9%84%20%D9%85%D8%B9%20%D8%AE%D8%AF%D9%85%D8%A9%20%D8%A7%D9%84%D8%B9%D9%85%D9%84%D8%A7%D8%A1,%D8%A7%D9%84%D8%AA%D8%AC%D9%85%D8%B9%20%D8%A7%D9%84%D8%A3%D9%88%D9%84%3A%200225983555...</t>
   </si>
   <si>
     <t>https://www.google.com/maps/search/لولو+هايبر+ماركت</t>
@@ -628,7 +644,7 @@
     <t>19619</t>
   </si>
   <si>
-    <t>https://metro-markets.com</t>
+    <t>https://www.metro-markets.com/</t>
   </si>
   <si>
     <t>https://www.google.com/maps/search/مترو+ماركت</t>
@@ -637,10 +653,21 @@
     <t>محمود الفار</t>
   </si>
   <si>
-    <t>16066</t>
-  </si>
-  <si>
-    <t>https://elfar-market.com</t>
+    <r>
+      <t>16778</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>https://mahmoudelfar.com/ar</t>
   </si>
   <si>
     <t>https://www.google.com/maps/search/محمود+الفار</t>
@@ -649,6 +676,23 @@
     <t>هايبر موسى</t>
   </si>
   <si>
+    <r>
+      <t>01128008047</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF474747"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>https://market.hypermousa.com/ar/</t>
+  </si>
+  <si>
     <t>https://www.google.com/maps/search/هايبر+موسى</t>
   </si>
   <si>
@@ -658,7 +702,7 @@
     <t>16404</t>
   </si>
   <si>
-    <t>https://hyperone.com.eg</t>
+    <t>https://www.hyperone.com.eg/ar/contact-us?srsltid=AfmBOopDOicIE0UMhRgoTC9z7G_sKJ8DZHUaAWWVXPtyjAv_mb6Z-n5n</t>
   </si>
   <si>
     <t>https://www.google.com/maps/search/هايبر1</t>
@@ -830,7 +874,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -847,6 +891,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="15"/>
+      <color rgb="FF040C28"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -855,8 +905,41 @@
     </font>
     <font>
       <u/>
+      <sz val="10.5"/>
+      <color rgb="FFFF0000"/>
+      <name val="Helvetica"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.5"/>
+      <color rgb="FF767676"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF474747"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF040C28"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -996,13 +1079,31 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="15"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1330,144 +1431,159 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="6" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="6" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="6" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1830,912 +1946,915 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
+    <row r="2" s="1" customFormat="1" ht="18.75" spans="1:6">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="5">
+        <v>15260</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" t="s">
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:6">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
+      <c r="B3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:6">
+      <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F3" t="s">
+      <c r="B4" s="9" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
+      <c r="C4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B4">
-        <v>16306</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="D4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:6">
+      <c r="A5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F4" t="s">
+      <c r="B5" s="1">
+        <v>16508</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
+      <c r="D5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B5" t="s">
+      <c r="E5" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C5" t="s">
+      <c r="F5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="2" t="s">
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:6">
+      <c r="A6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="B6" s="10">
+        <v>1007877779</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F5" t="s">
+      <c r="D6" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
+      <c r="E6" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="F6" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="18.75" spans="1:6">
+      <c r="A7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F6" t="s">
+      <c r="C7" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
+      <c r="D7" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B7" t="s">
+      <c r="E7" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C7" t="s">
+      <c r="F7" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:6">
+      <c r="A8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="B8" s="1">
+        <v>19279</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="D8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="F7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
+      <c r="E8" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B8" t="s">
+      <c r="F8" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C8" t="s">
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:6">
+      <c r="A9" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="B9" s="1">
+        <v>15120</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="D9" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="F8" t="s">
+      <c r="E9" s="8" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
+      <c r="F9" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B9" t="s">
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:6">
+      <c r="A10" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C9" t="s">
+      <c r="B10" s="1">
+        <v>19631</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D10" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E10" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F10" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
+    <row r="11" s="2" customFormat="1" spans="1:6">
+      <c r="A11" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C11" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E11" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F11" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
+    <row r="12" s="1" customFormat="1" spans="1:6">
+      <c r="A12" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B11">
-        <v>1011132252</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B12" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D11" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="3" t="s">
+      <c r="C12" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F11" t="s">
+      <c r="D12" s="6" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" t="s">
+      <c r="E12" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B12" t="s">
+      <c r="F12" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C12" t="s">
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:6">
+      <c r="A13" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="B13" s="1">
+        <v>16991</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="D13" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="F12" t="s">
+      <c r="E13" s="8" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" t="s">
+      <c r="F13" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B13" t="s">
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:6">
+      <c r="A14" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C13" t="s">
+      <c r="B14" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="C14" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="D14" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="F13" t="s">
+      <c r="E14" s="8" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" t="s">
+      <c r="F14" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B14" t="s">
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:6">
+      <c r="A15" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C14" t="s">
+      <c r="B15" s="1">
+        <v>16312</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D15" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E15" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F15" s="13" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:6">
+      <c r="A16" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" t="s">
+      <c r="B16" s="1">
+        <v>16642</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B15" t="s">
+      <c r="D16" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="C15" t="s">
+      <c r="E16" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="F16" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E15" s="3" t="s">
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:6">
+      <c r="A17" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F15" t="s">
+      <c r="B17" s="1">
+        <v>15677</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" t="s">
+      <c r="D17" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B16" t="s">
+      <c r="E17" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="C16" t="s">
+      <c r="F17" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D16" s="3" t="s">
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:6">
+      <c r="A18" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="B18" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="F16" t="s">
+      <c r="C18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="6" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" t="s">
+      <c r="E18" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="B17" t="s">
+      <c r="F18" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C17" t="s">
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:6">
+      <c r="A19" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="B19" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="C19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="F17" t="s">
+      <c r="E19" s="8" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" t="s">
+      <c r="F19" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B18" t="s">
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:6">
+      <c r="A20" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C18" t="s">
-        <v>57</v>
-      </c>
-      <c r="D18" s="3" t="s">
+      <c r="B20" s="1">
+        <v>15260</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E20" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F20" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:6">
+      <c r="A21" s="1" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" t="s">
+      <c r="B21" s="1">
+        <v>16232</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B19" t="s">
+      <c r="E21" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="C19" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="F19" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" t="s">
-        <v>106</v>
-      </c>
-      <c r="B20" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="F20" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" t="s">
-        <v>109</v>
-      </c>
-      <c r="B21">
-        <v>16232</v>
-      </c>
-      <c r="C21" t="s">
-        <v>40</v>
-      </c>
-      <c r="D21" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="F21" t="e" cm="1">
+      <c r="F21" s="1" t="e" cm="1">
         <f t="array" ref="F21">-(صفحة فيسبوك Geant.eg)</f>
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
-      <c r="A22" t="s">
+    <row r="22" s="1" customFormat="1" spans="1:6">
+      <c r="A22" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:6">
+      <c r="A23" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E23" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="B22" t="s">
+      <c r="F23" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" s="3" customFormat="1" spans="1:6">
+      <c r="A24" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C22" t="s">
-        <v>62</v>
-      </c>
-      <c r="D22" s="3" t="s">
+      <c r="B24" s="3">
+        <v>16821</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E24" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F24" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:6">
+      <c r="A25" s="1" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" t="s">
+      <c r="B25" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C25" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C23" t="s">
-        <v>74</v>
-      </c>
-      <c r="D23" s="3" t="s">
+      <c r="E25" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="F25" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="1:6">
+      <c r="A26" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="F23" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" t="s">
+      <c r="B26" s="1">
+        <v>19866</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="B24" t="s">
+      <c r="E26" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="C24" t="s">
-        <v>30</v>
-      </c>
-      <c r="D24" t="s">
-        <v>19</v>
-      </c>
-      <c r="E24" s="3" t="s">
+      <c r="F26" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="1:6">
+      <c r="A27" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="F24" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" t="s">
+      <c r="B27" s="1">
+        <v>17228</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B25" t="s">
-        <v>19</v>
-      </c>
-      <c r="C25" t="s">
-        <v>57</v>
-      </c>
-      <c r="D25" t="s">
-        <v>19</v>
-      </c>
-      <c r="E25" s="3" t="s">
+      <c r="D27" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="F25" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" t="s">
+      <c r="E27" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="B26" t="s">
+      <c r="F27" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="18.75" spans="1:6">
+      <c r="A28" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C26" t="s">
-        <v>62</v>
-      </c>
-      <c r="D26" s="3" t="s">
+      <c r="B28" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="C28" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="F26" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" t="s">
+      <c r="E28" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="B27" t="s">
+      <c r="F28" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="1:6">
+      <c r="A29" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C27" t="s">
+      <c r="B29" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="C29" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D29" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="E29" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="F27" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" t="s">
+      <c r="F29" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B28" t="s">
-        <v>19</v>
-      </c>
-      <c r="C28" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" t="s">
-        <v>19</v>
-      </c>
-      <c r="E28" s="3" t="s">
+    </row>
+    <row r="30" s="1" customFormat="1" spans="1:6">
+      <c r="A30" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="F28" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" t="s">
+      <c r="B30" s="1">
+        <v>16471</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B29" t="s">
+      <c r="E30" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="C29" t="s">
-        <v>86</v>
-      </c>
-      <c r="D29" s="3" t="s">
+      <c r="F30" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" spans="1:6">
+      <c r="A31" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="B31" s="1">
+        <v>16176</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D31" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="F29" t="s">
+      <c r="E31" s="8" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" t="s">
+      <c r="F31" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" spans="1:6">
+      <c r="A32" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B30" t="s">
-        <v>19</v>
-      </c>
-      <c r="C30" t="s">
-        <v>30</v>
-      </c>
-      <c r="D30" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="3" t="s">
+      <c r="B32" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="F30" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" t="s">
+      <c r="C32" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D32" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="B31" t="s">
+      <c r="E32" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="C31" t="s">
-        <v>74</v>
-      </c>
-      <c r="D31" s="3" t="s">
+      <c r="F32" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" spans="1:6">
+      <c r="A33" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="B33" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="F31" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" t="s">
+      <c r="C33" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D33" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="B32" t="s">
+      <c r="E33" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="C32" t="s">
-        <v>57</v>
-      </c>
-      <c r="D32" s="3" t="s">
+      <c r="F33" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="E32" s="3" t="s">
+    </row>
+    <row r="34" s="1" customFormat="1" spans="1:6">
+      <c r="A34" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="F32" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" t="s">
+      <c r="B34" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B33" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" t="s">
-        <v>62</v>
-      </c>
-      <c r="D33" s="3" t="s">
+      <c r="C34" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="E34" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F34" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" spans="1:6">
+      <c r="A35" s="1" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" t="s">
+      <c r="B35" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C35" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D35" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="C34" t="s">
-        <v>13</v>
-      </c>
-      <c r="D34" s="3" t="s">
+      <c r="E35" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="F35" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="F34" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" t="s">
+    </row>
+    <row r="36" s="1" customFormat="1" spans="1:6">
+      <c r="A36" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B36" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="C35" t="s">
-        <v>57</v>
-      </c>
-      <c r="D35" s="3" t="s">
+      <c r="C36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="E36" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F36" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="1" spans="1:6">
+      <c r="A37" s="1" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" t="s">
+      <c r="B37" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B36" t="s">
-        <v>117</v>
-      </c>
-      <c r="C36" t="s">
-        <v>30</v>
-      </c>
-      <c r="D36" t="s">
-        <v>19</v>
-      </c>
-      <c r="E36" s="2" t="s">
+      <c r="C37" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D37" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="F36" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" t="s">
+      <c r="E37" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="B37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" t="s">
-        <v>86</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="E37" s="3" t="s">
+      <c r="F37" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="F37" t="s">
+    </row>
+    <row r="38" s="1" customFormat="1" spans="1:6">
+      <c r="A38" s="1" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" t="s">
+      <c r="B38" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D38" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="C38" t="s">
-        <v>74</v>
-      </c>
-      <c r="D38" s="3" t="s">
+      <c r="E38" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="F38" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="39" s="1" customFormat="1" spans="1:6">
+      <c r="A39" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="F38" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" t="s">
+      <c r="B39" s="1">
+        <v>16806</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B39" t="s">
-        <v>19</v>
-      </c>
-      <c r="C39" t="s">
-        <v>62</v>
-      </c>
-      <c r="D39" s="2" t="s">
+      <c r="E39" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="E39" t="s">
-        <v>19</v>
-      </c>
-      <c r="F39" t="s">
+      <c r="F39" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="40" s="1" customFormat="1" spans="1:6">
+      <c r="A40" s="1" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" t="s">
+      <c r="B40" s="1">
+        <v>19482</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D40" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="B40" t="s">
+      <c r="E40" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="C40" t="s">
-        <v>57</v>
-      </c>
-      <c r="D40" s="3" t="s">
+      <c r="F40" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="41" s="1" customFormat="1" spans="1:6">
+      <c r="A41" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="B41" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="F40" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" t="s">
+      <c r="C41" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D41" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="B41" t="s">
+      <c r="E41" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="C41" t="s">
-        <v>86</v>
-      </c>
-      <c r="D41" s="3" t="s">
+      <c r="F41" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="E41" s="3" t="s">
+    </row>
+    <row r="42" s="1" customFormat="1" spans="1:6">
+      <c r="A42" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="F41" t="s">
+      <c r="B42" s="1" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" t="s">
+      <c r="C42" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D42" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="B42" t="s">
+      <c r="E42" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="C42" t="s">
-        <v>13</v>
-      </c>
-      <c r="D42" s="3" t="s">
+      <c r="F42" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="43" s="1" customFormat="1" ht="18.75" spans="1:6">
+      <c r="A43" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="B43" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="F42" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43" t="s">
+      <c r="C43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D43" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="B43" t="s">
+      <c r="E43" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="C43" t="s">
-        <v>30</v>
-      </c>
-      <c r="D43" s="2" t="s">
+      <c r="F43" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="44" s="1" customFormat="1" spans="1:6">
+      <c r="A44" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="B44" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="F43" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44" t="s">
+      <c r="C44" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D44" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="B44" t="s">
-        <v>19</v>
-      </c>
-      <c r="C44" t="s">
-        <v>57</v>
-      </c>
-      <c r="D44" t="s">
-        <v>19</v>
-      </c>
-      <c r="E44" s="3" t="s">
+      <c r="E44" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="F44" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45" t="s">
+      <c r="F44" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="45" s="1" customFormat="1" spans="1:6">
+      <c r="A45" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C45" t="s">
-        <v>62</v>
-      </c>
-      <c r="D45" s="2" t="s">
+      <c r="C45" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D45" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="E45" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="F45" t="s">
+      <c r="F45" s="1" t="s">
         <v>199</v>
       </c>
     </row>
   </sheetData>
+  <sortState ref="A2:F45">
+    <sortCondition ref="A10"/>
+  </sortState>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" display="https://www.google.com/maps/search/أسواق+فتح+الله"/>
     <hyperlink ref="E3" r:id="rId2" display="https://www.google.com/maps/search/اكسبشن+ماركت"/>
     <hyperlink ref="E4" r:id="rId3" display="https://www.google.com/maps/search/التوحيد+والنور"/>
-    <hyperlink ref="E5" r:id="rId4" display="https://www.google.com/maps/search/أسواق+الراية"/>
+    <hyperlink ref="E5" r:id="rId4" display="https://www.google.com/maps/search/أسواق+الراية" tooltip="https://www.google.com/maps/search/أسواق+الراية"/>
     <hyperlink ref="E6" r:id="rId5" display="https://www.google.com/maps/search/السلطان+ماركت"/>
     <hyperlink ref="E7" r:id="rId6" display="https://www.google.com/maps/search/حلواني+العبد"/>
     <hyperlink ref="E8" r:id="rId7" display="https://www.google.com/maps/search/أسواق+العثيم"/>
@@ -2774,41 +2893,40 @@
     <hyperlink ref="E42" r:id="rId40" display="https://www.google.com/maps/search/مترو+ماركت"/>
     <hyperlink ref="E43" r:id="rId41" display="https://www.google.com/maps/search/محمود+الفار"/>
     <hyperlink ref="E44" r:id="rId42" display="https://www.google.com/maps/search/هايبر+موسى"/>
-    <hyperlink ref="D45" r:id="rId43" display="https://hyperone.com.eg"/>
-    <hyperlink ref="D43" r:id="rId44" display="https://elfar-market.com" tooltip="https://elfar-market.com"/>
-    <hyperlink ref="D42" r:id="rId45" display="https://metro-markets.com"/>
-    <hyperlink ref="D41" r:id="rId46" display="https://luluhypermarket.com"/>
-    <hyperlink ref="D40" r:id="rId47" display="https://mywayegypt.com"/>
-    <hyperlink ref="D39" r:id="rId48" display="https://eg.avon.com" tooltip="https://eg.avon.com"/>
-    <hyperlink ref="D38" r:id="rId49" display="https://kazyon.com"/>
-    <hyperlink ref="D37" r:id="rId50" display="https://carrefouregypt.com"/>
-    <hyperlink ref="D35" r:id="rId51" display="https://elezabypharmacy.com"/>
-    <hyperlink ref="D34" r:id="rId52" display="https://misrpharmacies.com"/>
-    <hyperlink ref="D33" r:id="rId50" display="https://carrefouregypt.com"/>
-    <hyperlink ref="D32" r:id="rId53" display="https://centershaheen.com"/>
-    <hyperlink ref="D31" r:id="rId54" display="https://seoudisupermarket.com"/>
-    <hyperlink ref="D29" r:id="rId55" display="https://spinneys-egypt.com"/>
-    <hyperlink ref="D27" r:id="rId56" display="https://salesucre.com"/>
-    <hyperlink ref="D26" r:id="rId57" display="https://zahranmarket.com"/>
-    <hyperlink ref="D23" r:id="rId58" display="https://raneen.com"/>
-    <hyperlink ref="D22" r:id="rId59" display="https://kheirzaman.com"/>
-    <hyperlink ref="D20" r:id="rId60" display="https://fathallahg.com"/>
-    <hyperlink ref="D19" r:id="rId61" display="https://tseppas.com"/>
-    <hyperlink ref="D18" r:id="rId62" display="https://bim.eg"/>
-    <hyperlink ref="D17" r:id="rId63" display="https://baitelgomla.com"/>
-    <hyperlink ref="D16" r:id="rId64" display="https://panda.com.eg"/>
-    <hyperlink ref="D15" r:id="rId65" display="https://etoile.com.eg"/>
-    <hyperlink ref="D14" r:id="rId66" display="https://awladragab.com"/>
-    <hyperlink ref="D13" r:id="rId67" display="https://oscarstores.com"/>
-    <hyperlink ref="D12" r:id="rId68" display="https://el-morshedy.com"/>
-    <hyperlink ref="D10" r:id="rId69" display="https://elfergany.com"/>
-    <hyperlink ref="D9" r:id="rId70" display="https://alfa.com.eg"/>
-    <hyperlink ref="D8" r:id="rId71" display="https://othaimmarkets.com"/>
-    <hyperlink ref="D7" r:id="rId72" display="https://elabddelivery.com"/>
-    <hyperlink ref="D5" r:id="rId73" display="https://elrayamarket.com" tooltip="https://elrayamarket.com"/>
-    <hyperlink ref="D3" r:id="rId74" display="https://exceptionmarket.com"/>
-    <hyperlink ref="D2" r:id="rId60" display="https://fathallahg.com"/>
-    <hyperlink ref="E45" r:id="rId75" display="https://www.google.com/maps/search/هايبر1"/>
+    <hyperlink ref="D45" r:id="rId43" display="https://www.hyperone.com.eg/ar/contact-us?srsltid=AfmBOopDOicIE0UMhRgoTC9z7G_sKJ8DZHUaAWWVXPtyjAv_mb6Z-n5n" tooltip="https://www.hyperone.com.eg/ar/contact-us?srsltid=AfmBOopDOicIE0UMhRgoTC9z7G_sKJ8DZHUaAWWVXPtyjAv_mb6Z-n5n"/>
+    <hyperlink ref="D43" r:id="rId44" display="https://mahmoudelfar.com/ar" tooltip="https://mahmoudelfar.com/ar"/>
+    <hyperlink ref="D42" r:id="rId45" display="https://www.metro-markets.com/" tooltip="https://www.metro-markets.com/"/>
+    <hyperlink ref="D40" r:id="rId46" display="https://mywayegy.co/" tooltip="https://mywayegy.co/"/>
+    <hyperlink ref="D38" r:id="rId47" display="https://okaziooun.com/shop/contact-us/" tooltip="https://okaziooun.com/shop/contact-us/"/>
+    <hyperlink ref="D37" r:id="rId48" display="https://carrefouregypt.com"/>
+    <hyperlink ref="D35" r:id="rId49" display="https://elezabypharmacy.com"/>
+    <hyperlink ref="D34" r:id="rId50" display="https://misr-online.com/" tooltip="https://misr-online.com/"/>
+    <hyperlink ref="D33" r:id="rId51" display="https://www.supeco.app/index.html" tooltip="https://www.supeco.app/index.html"/>
+    <hyperlink ref="D32" r:id="rId52" display="https://shaheeneg.com/ar/" tooltip="https://shaheeneg.com/ar/"/>
+    <hyperlink ref="D31" r:id="rId53" display="https://seoudisupermarket.com"/>
+    <hyperlink ref="D29" r:id="rId54" display="https://spinneys-egypt.com"/>
+    <hyperlink ref="D27" r:id="rId55" display="https://salesucre.com"/>
+    <hyperlink ref="D26" r:id="rId56" display="https://zahranmarket.com"/>
+    <hyperlink ref="D23" r:id="rId57" display="https://raneen.com"/>
+    <hyperlink ref="D22" r:id="rId58" display="https://kheirzaman.com"/>
+    <hyperlink ref="D19" r:id="rId59" display="https://tseppas.com"/>
+    <hyperlink ref="D18" r:id="rId60" display="https://bim.eg"/>
+    <hyperlink ref="D15" r:id="rId61" display="https://etoileeg.online/" tooltip="https://etoileeg.online/"/>
+    <hyperlink ref="D14" r:id="rId62" display="https://awladragab.com"/>
+    <hyperlink ref="D13" r:id="rId63" display="https://oscarstores.com"/>
+    <hyperlink ref="D12" r:id="rId64" display="https://www.facebook.com/Al.morshedy/?locale=ar_AR" tooltip="https://www.facebook.com/Al.morshedy/?locale=ar_AR"/>
+    <hyperlink ref="D10" r:id="rId65" display="https://www.facebook.com/marketelfergany/?locale=ar_AR" tooltip="https://www.facebook.com/marketelfergany/?locale=ar_AR"/>
+    <hyperlink ref="D9" r:id="rId66" display="https://www.facebook.com/AlfaMarketeg/#:~:text=in%20no%20time.-,%F0%9F%93%9E%2015120%20%F0%9F%8C%90%20www.alfamarketeg.com%20%F0%9F%93%B1%20Download%20Alfa,Market%20App%20%2D%20%D8%AD%D9%85%D9%84%20%D8%A7%D9%84%D8%A7%D8%A8%D9%84%D9%83%D9%8A%D8%B4%D9%86%20%23NoTricksJustTreats" tooltip="https://www.facebook.com/AlfaMarketeg/#:~:text=in%20no%20time.-,%F0%9F%93%9E%2015120%20%F0%9F%8C%90%20www.alfamarketeg.com%20%F0%9F%93%B1%20Download%20Alfa,Market%20App%20%2D%20%D8%AD%D9%85%D9%84%20%D8%A7%D9%84%D8%A7%D8%A8%D9%84%D9%83%D9%8A%D8%B4%D9%86%20"/>
+    <hyperlink ref="D8" r:id="rId67" display="https://othaimmarkets.com"/>
+    <hyperlink ref="D7" r:id="rId68" display="https://elabdfoods.com/" tooltip="https://elabdfoods.com/"/>
+    <hyperlink ref="D5" r:id="rId69" display="https://www.facebook.com/AlRayahMarketEg/" tooltip="https://www.facebook.com/AlRayahMarketEg/"/>
+    <hyperlink ref="D3" r:id="rId70" display="https://exception.com.eg/" tooltip="https://exception.com.eg/"/>
+    <hyperlink ref="D2" r:id="rId71" display="https://www.facebook.com/aswaqfathallamarket/posts/%D8%A3%D8%B7%D9%84%D8%A8-15260-%D9%88-%D8%B7%D9%84%D8%A8%D8%A7%D8%AA%D9%83-%D8%AA%D8%AC%D9%8A%D9%84%D9%83-%D9%84%D8%AD%D8%AF-%D8%A8%D8%A7%D8%A8-%D8%A8%D9%8A%D8%AA%D9%83-%D9%81%D8%AA%D8%AD_%D8%A7%D9%84%D9%84%D9%87_%D8%AF%D8%A7%D9%8A%D9%85%D8%A7_%D8%A7%D9%84%D8%A3%D9%82%D8%B1%D8%A8_%D9%88_%D8%A7%D9%84%D8%A3%D9%88%D9%81%D8%B1/2195360477437969/" tooltip="https://www.facebook.com/aswaqfathallamarket/posts/%D8%A3%D8%B7%D9%84%D8%A8-15260-%D9%88-%D8%B7%D9%84%D8%A8%D8%A7%D8%AA%D9%83-%D8%AA%D8%AC%D9%8A%D9%84%D9%83-%D9%84%D8%AD%D8%AF-%D8%A8%D8%A7%D8%A8-%D8%A8%D9%8A%D8%AA%D9%83-%D9%81%D8%AA%D8%AD_%D8%A7%D9%84%D9%"/>
+    <hyperlink ref="E45" r:id="rId72" display="https://www.google.com/maps/search/هايبر1"/>
+    <hyperlink ref="B3" r:id="rId73" display="01200 9622 2" tooltip="https://exception.com.eg/tel:+201200962222"/>
+    <hyperlink ref="F15" r:id="rId61" display="https://etoileeg.online/"/>
+    <hyperlink ref="D41" r:id="rId74" display="https://www.facebook.com/LuLuHypermarketEG/?locale=ar_AR#:~:text=%D8%AA%D9%82%D8%AF%D8%B1%20%D8%AA%D8%AA%D9%88%D8%A7%D8%B5%D9%84%20%D9%85%D8%B9%20%D8%AE%D8%AF%D9%85%D8%A9%20%D8%A7%D9%84%D8%B9%D9%85%D9%84%D8%A7%D8%A1,%D8%A7%D9%84%D8%AA%D8%AC%D9%85%D8%B9%20%D8%A7%D9%84%D8%A3%D9%88%D9%84%3A%200225983555..."/>
+    <hyperlink ref="D44" r:id="rId75" display="https://market.hypermousa.com/ar/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -2856,15 +2974,15 @@
         <v>201</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>202</v>
@@ -2873,15 +2991,15 @@
         <v>203</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B4">
         <v>16119</v>
@@ -2890,15 +3008,15 @@
         <v>204</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
         <v>205</v>
@@ -2907,32 +3025,32 @@
         <v>206</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
         <v>207</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
         <v>208</v>
@@ -2941,15 +3059,15 @@
         <v>209</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s">
         <v>210</v>
@@ -2958,15 +3076,15 @@
         <v>211</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B9">
         <v>15120</v>
@@ -2975,15 +3093,15 @@
         <v>212</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B10">
         <v>19631</v>
@@ -2992,15 +3110,15 @@
         <v>213</v>
       </c>
       <c r="D10" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B11" t="s">
         <v>214</v>
@@ -3009,15 +3127,15 @@
         <v>215</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B12">
         <v>16901</v>
@@ -3026,15 +3144,15 @@
         <v>216</v>
       </c>
       <c r="D12" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E12" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B13">
         <v>16991</v>
@@ -3043,15 +3161,15 @@
         <v>217</v>
       </c>
       <c r="D13" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E13" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B14">
         <v>19225</v>
@@ -3060,10 +3178,10 @@
         <v>218</v>
       </c>
       <c r="D14" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E14" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -3077,15 +3195,15 @@
         <v>220</v>
       </c>
       <c r="D15" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E15" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B16">
         <v>16642</v>
@@ -3094,15 +3212,15 @@
         <v>221</v>
       </c>
       <c r="D16" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="E16" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B17">
         <v>15677</v>
@@ -3111,15 +3229,15 @@
         <v>222</v>
       </c>
       <c r="D17" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="E17" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="B18" t="s">
         <v>223</v>
@@ -3128,15 +3246,15 @@
         <v>224</v>
       </c>
       <c r="D18" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="E18" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B19">
         <v>19918</v>
@@ -3145,15 +3263,15 @@
         <v>225</v>
       </c>
       <c r="D19" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="E19" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="B20" t="s">
         <v>226</v>
@@ -3162,10 +3280,10 @@
         <v>227</v>
       </c>
       <c r="D20" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="E20" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -3183,12 +3301,12 @@
         <v>#NAME?</v>
       </c>
       <c r="E21" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B22">
         <v>16007</v>
@@ -3197,112 +3315,112 @@
         <v>230</v>
       </c>
       <c r="D22" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="E22" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C23" t="s">
         <v>231</v>
       </c>
       <c r="D23" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E23" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C24" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D24" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E24" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D25" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E25" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C26" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D26" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E26" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C27" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D27" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E27" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C28" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D28" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E28" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -3316,66 +3434,66 @@
         <v>234</v>
       </c>
       <c r="D29" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="E29" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="B30" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C30" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D30" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E30" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B31" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C31" t="s">
         <v>235</v>
       </c>
       <c r="D31" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E31" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C32" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D32" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E32" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B33" t="s">
         <v>236</v>
@@ -3384,15 +3502,15 @@
         <v>237</v>
       </c>
       <c r="D33" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="E33" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B34" t="s">
         <v>238</v>
@@ -3401,15 +3519,15 @@
         <v>235</v>
       </c>
       <c r="D34" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E34" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B35" t="s">
         <v>239</v>
@@ -3418,32 +3536,32 @@
         <v>240</v>
       </c>
       <c r="D35" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E35" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B36" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C36" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D36" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E36" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B37" t="s">
         <v>241</v>
@@ -3452,32 +3570,32 @@
         <v>242</v>
       </c>
       <c r="D37" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E37" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B38" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C38" t="s">
         <v>243</v>
       </c>
       <c r="D38" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E38" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B39" t="s">
         <v>244</v>
@@ -3486,15 +3604,15 @@
         <v>245</v>
       </c>
       <c r="D39" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E39" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B40" t="s">
         <v>246</v>
@@ -3503,15 +3621,15 @@
         <v>245</v>
       </c>
       <c r="D40" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E40" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B41" t="s">
         <v>247</v>
@@ -3520,61 +3638,61 @@
         <v>248</v>
       </c>
       <c r="D41" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E41" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B42" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C42" t="s">
         <v>249</v>
       </c>
       <c r="D42" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E42" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B43" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C43" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D43" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E43" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B44" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C44" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D44" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E44" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -3591,7 +3709,7 @@
         <v>199</v>
       </c>
       <c r="E45" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
